--- a/backend/data/tickets_details.xlsx
+++ b/backend/data/tickets_details.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -467,9 +467,27 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>HDL-TKT000003</v>
+      </c>
+      <c r="B5" t="str" xml:space="preserve">
+        <v xml:space="preserve">&lt;p&gt;teste&lt;br&gt;&lt;img src="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAdcAAAD3CAIAAADAPYkUAAAQAElEQVR4Aezdb2wcZX7A8WfW9q7/xE4cHGyTHE4sOKmH015ouNyhEqFI1+oQB4UqqCqlESXoUCXgBQEk+oLmBahAeEF5kxPHIYsDqUkL5A4FnWgR8kncIUXiVAynQhQIBeWfSUJsX7Adsv09zzOz/3e9f2Z2Zna/o/F6d+aZ589nyG+f/c2sSfSyIIAAAgiEJ5BQLAgggAAC4QnkReHenrVDq/9s3dpr1q+/ZnycFQEEEGg5gTAi24YN14xd/r3R4WsG+zf1d393oHdTf8/VA71/PtC7eWXfNW4U7um+bPjS742MDveuWEx1zyWTc6kUKwIIIICADwLJ5Gyi41yye271pWpgMCnTbkddVCrtqLQ86ijc3/ftNZeu61txvrPzj319KplUHR1SjBUBBBBAwAeBRMLp7nZ6e1UicT7V88fBoc6OTonAFy+m0yqdTvT2XLn6kpUdHRLvL3R0OD40SBUIIICAK8CvPIHOTieV+qajY35gsFM5sshkOJ0YGBjs6Fzo7paJcV5pXiCAAAIIBCGQ6k53dn3dv7IrndZ5iUTfCgnMS0G0RJ0IIIAAAiUFEoml7t6lri7JS6QTFy9+3dlZshgbEUAgZgJ0Ny4CnZ1OOr2Y6umULESio0OmxHHpOf1EAAEEWkbgm2RKLsWlE11dLTMkBoIAAgjERkBib6JDpsJpfadabHpNRxGIlACdQaABgURC3yMhFRCFBYEVAQQQCEkgzVw4JHmaRQABBERAUhLMhcWBNRYCdBKB1hQgCrfmeWVUCCAQEwEyEjE5UXQTAQRaVMBhLtyiZ7bhYVEBAgg0RYC5cFOYaQQBBBAoJ1DTXHj+hWcOv1WwPn72tnJ1V7H9trs/kwp/eXepP2Sx+ewvpa3G6q+iC9kilTqTLcUzBBBoukDPxfvuOfYfuz8vvT5yetdEAF3quXjXnSdevn/2tuESlV/xp/PPPnLs6RsujNUUREvUpBquoG/mnmdO7CpVNdtqEKAoAghUEOi82D+wpE4MTr0z9F/569T/9KpVs1f/8PS/XH9xpEINdexKqK7UhZHxE/9457nb16rc5aqr5x/622NXDS/1d6rGv32cyK26uuf9B++/Ypu7jh7Vx8xuLTmZ1bv4QQABBHwRcGa/TB34dffe/HXfdGpWLY2sPz2x4cIldcSzCl2bT+x9cXTfH7qToyfv2PHVXZe7RTd9f3bXbceu6EsefvuyJ1/vPNzwX+JpsNd9d744NKfUig3zbl7ilhOSYcisL9zi9luppacfz8lmPDSf2WGf2GyAPrBo1+Uma6F35U+6dz2UrTAvp2FTGZLNMGtmly3/wt0m0fHMYdu3bLuPn/WQbY94RACBthfQgfiy1yQQD5/a/g9n7xpXW/7i3IO3nhjrMSH4gA8hWIgbjMJKHer6UqrpW9AhTMLf9bPyKrOOXW+TFRKCj27qy2xWau2xTHDUWzccu2diUT+Rn4JdfTM3ZHap2RvcNLFUePiGnM8IKyaOvuWG7/kX7phZIfV464qJY09v9l4oNTYxs0LJy+Tp/1MSgrPt5jUkBVgRQAABpSQQvzTy2v92J9fM3H7PZ//8NydHUsnDU6NP+hSC3f/vnB/SC6MS6Q6tusnNVFyx7X6brDDb3QaS770o2931puey6ZQVfSmb5dg7nZSyKwa9iCwvlDr6tj3EVNg38yOZX99y2sR0r0IzH1drvzTRtu/ObB/G3tNz7sXV3zIV2Yf5ob26wOUPHFraskE3NDc9ZhIspn5bhkcEEEDAE1ic7dz7og7EKrW4IqFD8DOvdjWeiPCqb/zqXKam7BN7K8WxseyWrnc/kfC6uOkOm0P4zITL7G71xYo95tW+mZT5nfMwP/TGq/Zl3wdf6CeXDC3dNrQgz+amRx84JL9lPr5qSu9avHJT5l4LPVl+65n8CbgpO/dJ3z7zRKnF1Xp63j/lvh/0vWHeA9yd/EIAAQQ8gas2nt+0/mvzavHyP5n/vv7sb1758dBwRmLz0iW6H6ljEhAlIyGp2MeX3tCTzezUUvbve+5ymW/aqa6EPx2O3QSC7FRzZyRG6yd+/Nj3gNPHHpEZtJ0L59X65Ux2Dp63gxcIIIBAKQG5HHffTSfGUl1Hf7f2v4+kJDWx/e+/umt9qaJ1bWswCi89fatOws5Nr5bJ7K5t5rmdbLrROa9TNhZvcxMIc7vydpZ5YVMQeuf8VSYRLGHUTpmzCd/NZ7fqXcmP3+u67e4v9RzcnVzb2a4+uNRP8rTOV2Ru8Jj/UTYBXao42xBAoP0EdAj+6xP2ctyef+956uejJkd8avvfZe+aaFCljig8e4NMeN3VfuR3P9R/Zqa0+kKZ7M27RGbnpzYdcfgtu8sNlMv3f+x6e6BJcdgExaurbcJXz6kzbX1xiSQobICWq3/mngpzSNkWbJ5EuR1+pnLhsrWwAwEEmiGQWBq79tPiL469/E/HxooSmX71Z9Pm2fskBKdSH7x52ZMHuj64qCRH/G8vXLZvuic5fEpmxLeXTk3U1n4dUTi/gS9Gt90/LBNh2brvuVETHOWpkkteJv9gc7VyxSw/OSCXyJ7USVldtPLP/NDBTLpWjnpklcnqdj3wyBUHdS7YPVia22YrfHU4u1369na/lBi7Uk965UnBKnNz00mzObchs4EHBBCIisBs52P/Ov7Y2wP6enqz+pRcs3TzX54aS3V/8ObonoM5N6WdT+z9xehLv+9Tw6du+auFTZ2qwaWmKCzBVJKt+auNfW4vdHCU/K+sNz3XJTHOPjE7s7tk4zY3mKr8Mkq9Oqz32jrtHRePrNpjcsp6u3eUqVDteTLbE2nObpTH7HapJ6dCu/1O91qfFNSr7YCt3DaUW5UuwQ8CCERD4PB7g/tfX7fvYKn19XWv/q7zaMNfoMgd6OKprl/sX/fSS5c9drCo5vOJ518e3vuf3/r5a6n3LuQeVM/zmqJwPQ1wDAIIIOCLwNFPu55/s/C7c3t/3a2/Tfdm90t/SMz50kxOJYc/Tj5/KHE8Z0v26ULitanUwVPZDfU+c4jC9dJxHAIIIOCDQJoo7IMiVSCAAAJ1CxCF66bjQATaUoBB+y1AFPZblPoQQACBWgSIwrVoURYBBBDwW4Ao7Lco9SHgpwB1tb4AUbj1zzEjRACBKAsQhaN8dugbAgi0vgBRuPXPMSOsXoCSCDRfgCjcfHNaRAABBLICROGsBc8QQACB5gsQhZtvToueAL8RQEAF8n88whUBBBBAoFoB5sLVSlEOAQQQCEIgscDSLgKMEwEEoiVgYzpzYevAIwIIIBCOAFE4HHdaRQABBKwAUdg6+P9IjQgggEA1AkThapQogwACCAQlQBQOSpZ6EUAAgWoEWiUKVzNWyiCAAALREyAKR++c0CMEEGgngXCicE9Pz8qVK4eGhoaHh0dYEEAAgTAEJP5IFJJYJBEpxLBfXxSuv8O9vb1r1qxJpVKLi4tnz549efLkcRYEEEAgDAGJPxKFJBZJRJK4JNGp/tDWwJHNi8KO4wwODspoZdiynj9//sKFC+l0uoHOcygCCCBQv4DEH4lCEoskIskq0UlilESq+mus68gmRWEZ2OrVq2XAZ86cWVpaqqurHIQAAggEJSBxSaKTxCiJVBKvCpsJ8nWTovCqVatk2j87OxvkWKgbAQQQaEhAYpREKolXDdVS48HNiMI22yLDq7FvFEcAAQSaLWAjlY1azWm7GVG4r69vbm6uOeOhFQQQiL9AyCOQeCVRq2mdCDwK9/T0SMJF1qYNiYYQQACBRgQkXskqsauRSqo91gn+/7WRTCYXFhYUCwIIIBAfAYlaErua0d908FG4q6tL3lWaMRjaQACBugQ4qFhAopbEruLtQWwJPCPR0dHxzTffBNF16kQAAQQCEpCoJbEroMoLqg08CjuOk+arGQXqvEQAgWgLSNSS2NWcPgYehZszDFpBIDYCdBSBfAGicL4HrxBAAIHmChCFm+tNawgggEC+AFE434NXrSbAeBCIugBROOpniP4hgEBrCxCFW/v8MjoEEIi6AFE46mcoXv2jtwggUKsAUbhWMcojgAACfgoQhf3UpC4EEECgVgGicK1iUSpPXxBAIP4CROH4n0NGgAAC8RVwgv+baooFAQQQQKCcQBP+smW5pmO4nS4jgAAC/guQkfDflBoRQACB6gWIwtVbURIBBBDwXyC6Udj/sVIjAgggED0BonD0zgk9QgCBdhIgCrfT2WasCCAQPQEvCkevZ/QIAQQQaAcBonA7nGXGiAAC0RUgCkf33NAzBBAITiA6NROFo3Mu6AkCCLSjAFG4Hc86Y0YAgegIEIWjcy7oCQKtK8DIygsQhcvbsAcBBBAIXoAoHLwxLSCAAALlBBz+sqViQaD1BBhRfAT4y5bxOVf0FAEEWlOAjERrnldGhQACcREgCsflTNHP6ArQMwQaESAKN6LHsQgggECjAq0RhRd/9vz0+/un339qtlEP7/jdT5kKn5/ZYbbsePhjXf/+6QP2tdlY28OOz00NH/9sa23H+V169oBAyeoNzcf6C9DK1xxgH8o3yh4EIioQ8Sjs/XOVqJG7FkTbree+M2B813+12/xu+GH2u+tNHQNnrvMpaO6eOGtqXPjODxbNk0oPXtC3IVsQ7JNKhwS+b+vMO7mnoOC5jun+o5UeFFsRaC2BiEfhMtjrj8q8MjstnRr48Jwp+enKR83vSg8mmrzzcOVQ2P/7T00d5wZ/M2WeNPzw6PQqU0fqw98mzZMKD7O3bl4wuxe23CtT8qPjqucLn7phqg3owX+0ch0171IReGcq1z+2I1CLQEyi8LmRPdsnNpr1FRsflRq/MfPvMLnzLrP3wf5lxi5pgXuPL1dI1/Hog6bCu4Ym9Ss/fibXmf5fuXPZeLp1YY1KvfvsxMZnR2yGZfbQpcu/u/jRx0p1TA1da/xlFN4pMJ20Gw2U/2ilOiR5j12b7btUqd1sQyBuAjGJwjms8k/diwILW35sw1TO7hZ4quOdCdb6iX4zuPaJZafPwQ2bmhFAIFiB+EVh8Xj0V+4kUbmJYMmcyif36fd1dlL2y+ptcdOXn+9W5grejTY5q/o3fyQ5DZOX8Eo+P7PbXoLTlZjC+lg5UGrLW2UuJseaNTMZV+Yzsu5DJk9SsKXgpVujzM11K/pAqdD0J1uVbDFrthX3KJNUMbvMgbrD7p6SvzJNyyGZ7uWVzKuwqLm8ohVelEbLbb1MBzIH5lxfLdkls/FWm7JXNl3j9ragFStZoa/sQiA6ArGMwmoqdcolPL+2+OqZ/rcquVS3RLW/Bo572dhKR4zfOO1FASkmgcCNAvKi1lVHc+9dIffY8aGCj9t5rehwU5BUGTi+a3/ZbkgruZ/fx28slCmqUJpr4FaQ3JGYd77c1vN2ei92PHx0i724+unYRpNTqrVLBWP0KuY3AvEQiGcUVqlT9nJcKeQdPzhjM79HXtcf5708pskdv24vkanZQ9+W7QWf9O3Ge24Q4AAACzpJREFUjSbFWapis83LUO85lDKv68yKSKBxo7lX4cbtYx8qJXVKykX65q5uati7s2LrzE/clOiqV2xC1iuwZYd7U53UkF23zvzQnTm65b1ue0W8Ct2xb5+w2Z7xraVq8w6q8vfupz7Khlevt97bp1eH1wElDiYEK29LiS6ZFI3tobKp8+2SuvHuzZAayrXitcZvBCIoENMovLDGzp5K3TwwebzHQsu81eYoHn1wXRVXt1a9WUX69ciUe71u8omRI7aZ1Qu130O8eN237YQ39e6kW6FS/TtzOiDzO/n8/r437e03E+ScNxhvRFNDb9rLlaVuqisun+226XymgE3RSIvue8PA1+OmQAMPXnBUq16x4VXqmhramX+587of24ulWYfau+S9JevPBGYWPzV0c46kNMuKQJQF4hmFty6ssajnut1QaF/ax8l13nRJKfMv08Ziu7PsY8mqypb2a0fxLWhuktSNhn61U3M9pVI9NVdiDqgAO3B8i52qV3VHYLkuJXdOetcJ9J0zOldeOv1tusMDAtEScOL5ly13uxMoNfvRQP7UStnFfqjPfvoeOP6TkjcI29L1PWbeCU6nSvahKL1bXTM7TuZ/ih8r8TZTXU01lcpkb9xMiP6kX1MFdRU+N/KKTeyUOkE1dMlkKiSlk7Eav7HEZdW6ushBCAQsEMO/bKmniu488dzIT0t98JSUq50KTT5xZeaWW/uJPsNZ8DKzfdknmYRp9p1gJiVHTWbSIBP25rnM53HZWbwmf/ORPkqps7dm7nDYOnPg4cUdI+dN6dS7vzLJ7R1f5WYGJn87aGvPdEOyqG7mt9R0MtsrL8+7+6m8q3PZCnPD1o7PLaDpSd0P3pc45ONI5ruORTUfeWLsXZPi79981H63u+ouLazZYPs2e8A17L/Zy2srVW7ibA/hEYEICcQkIyH/kt07urwLPpJtLH8ZTWeEbXkvr3pk2gS1T7ptFFPm23f13M/k9aTwnWBypTsRMzW/vz8v2BWf8Ekv+rg5E+ntvcclzeLFTX2jgmRp3y+4iWJq6KeHTPj2uuEljrN51by2Ji+1MS7TitvtTKFMWlneD6QPdi1oNFO4xiePPuhN5F2T6cLh6AqTO6fsJVMZspnALtelI+ZtTw41Z9ncHJLR2O/dwVLqPUkOYUUgggLNjMK+Dd98VvUuTy1fq7494GabNZCPrt5tEssfV6rEkde9yCJ75aJ89p2g/2b3dgXZoe/ByOZD9IbiH33PRkGZU8eTanJdzkbpeU5zpo7cCb7ZoPTdBWUTCLqVbJZc31dQWKHO3hSYnBt5xXK5DdT9K3dyaitJnfrEPsl5zObx3U8GlbskAjkjyqnHe6pvrsieF28rvxGIqkDEo7D+Z+xlKt3bzuSlG1Kzpl4x829P/pVKmZw1P1673yTWtZk71fKO9arUwcvU4B6bqfPmSa/89onCe9okxMtGs0rNOYfoWgte6k1K6Y06ArpfBbbj0htNJRu3S+tec5nbDOTInIZ0J82oZXO5VQc1t8Ird055FeYelWNSS4VSW26bhWh2X07rYm4PKexDtkymVxW7lC2v33682twxTgi+bZpHBGIhEPEoHAvDxjspH8ZzvjbWeH3UgAACURCorg9E4eqcgiulJ30mS1DPfcfBdYuaEUCgSQJE4SZBl2vGfDtDX8rLfB+kXEm2I4BASwoQhUM+rZkUp00Kh9wbmkcgxgJx7TpROK5njn4jgEBrCBCFW+M8MgoEEIirAFE4rmeOfiMQrgCt+yVAFPZLknoQQACBegSIwvWocQwCCCDglwBR2C9J6kEgSAHqblUBJ55/2VKxIIAAAq0hEMO/bNka8IwCAQQQcAXISLgQ/EIgR4CnCDRPgCjcPGtaQgABBIoFiMLFJmxBAAEEmidAFG6eNS2VE2A7Au0sQBRu57PP2BFAIHwBonD454AeIIBAOwsQhdvv7DNiBBCIkgBROEpng74ggED7CRCF2++cM2IEEIiSAFE46LNB/QgggEAlAaJwJR32IYAAAkELEIWDFqZ+BBBAoJJAq0XhSmNlHwIIIBA1AYe/bKlYEEAAgfAE+MuW4dnTMgIIIKAFGstI6Br4QQABBBCoX4AoXL8dRyKAAAKNCxCFGzekBgQQaBeBIMZJFA5ClToRQACBagWIwtVKUQ4BBBAIQoAoHIQqdSKAgB8C7VEHUbg9zjOjRACBqAoQhaN6ZugXAgi0hwBRuD3OM6NEYHkBSoQh4PANZsWCAAIIhCfAN5jDs6dlBBBAQAuQkdAK/CDQfAFaRMAKEIWtA48IIIBAGAIOeWHFggACCIQnQF44PHtabq4ArSEQVQEyElE9M/QLAQTaQ4Ao3B7nmVEigEA0BRzywoolCAHqRACB6gTIC1fnRCkEEEAgKAEyEkHJUi8CCCBQjQBRuBqlqJehfwggEF8BonB8zx09RwCBVhAgCrfCWWQMCCAQXwGicO3njiMQQAABvwQc7lRTLAgggEB4AtypFp49LSOAAAJaIPoZCd1LfhBAAIFWFSAKt+qZZVwIIBAHAYe8sGJBAAEEwhMozguH1xdaRgABBNpRgIxEO551xowAAtERIApH51zQEwQQaL5A2C065IUVCwIIIBCeAHnh8OxpGQEEENACZCS0Aj8IINAcAVopFiAKF5uwBQEEEGieAFG4eda0hAACCBQLEIWLTdiCQKsIMI44CBCF43CW6CMCCLSqgMOdaooFAQQQCE+AO9XCs6fl1hNgRAjULuAwF1YsCCCAQHgCzIXDs6dlBBBAQCmHubBiiasA/UagFQSYC7fCWWQMCCAQZwHuVIvz2aPvCCAQfwGicPzPYXNGQCsIIBCEgENeWLEggAAC4QmQFw7PnpYRQAABxT0SKqoL/UIAgfYQYC7cHueZUSKAQHQFuDoX3XNDzxBAoPUFHK7OKb3wgwACCIQjQEYiHHdaRQABBKyAw1xYsSCAAALhCYQzFw5vvLSMAAIIREvAYS6sWBBAAIEwBbhHIkx92kYAgXYQqDxGonBlH/YigAACQQqk00ThIH2pGwEEEKgs4DhE4cpC7EUAgbgJxKu/3CMRr/NFbxFAoNUEHO6RUCwIIIBAeALkhcOzp2UEWkOAUTQmQF64MT+ORgABBBoV4Opco4IcjwACCNQvQEaifjuORCAMAdpsNQEyEq12RhkPAgjES4A71eJ1vugtAgi0moDDnWqKBYHyAuxBIGgB8sJBC1M/AgggUEmAvHAlHfYhgAACwQtwp1rwxrRQrQDlEGhHAaJwO551xowAAlERIC8clTNBPxBAoD0FyAu353m3o+YRAQQiIMBfeY/ASaALCCDQxgL8lfc2PvkMHQEEwhcgL9y8c0BLCCCAQLEAeeFiE7YggAACTRQgL9xEbJpCAAEECgVa96/5FI6U1wgggEAUBRz+mo9iQQABBMIU4LtzYerTNgIItL2AT3eqtb0jAAgggEBdAtypVhcbByGAAAI+CTjkhRULAgggUKuAn+XJC/upSV0IIIBATQKOIi9cExiFEUAAAV8F0uSFffWkMgQQCESglSt1yAsrFgQQQCBMAfLCYerTNgIItL0AeeG2/08AAAQKBXjdTAHyws3Upi0EEECgUMAhL6xYEEAAgTAFyAuHqU/bCCiFQXsL8Jct2/v8M3oEEAhbwCEjoVgQQACBMAXISISpT9vNF6BFBCIl4CjmwpE6IXQGAQTaTYC8cLudccaLAALREnCYCyuWIAWoGwEElhMgL7ycEPsRQACBAAX4BnOAuFSNAAIILCdAXng5oXjtp7cIIBA3AYe8sGJBAAEEwhQgLxymPm0jgAACROH6/xvgSAQQQKBRgbTz/wAAAP//sfjAaQAAAAZJREFUAwCVpgaEXYa7lQAAAABJRU5ErkJggg=="&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;</v>
+      </c>
+      <c r="C5" t="str">
+        <v>15/04/2026</v>
+      </c>
+      <c r="D5" t="str">
+        <v>gestor1</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
   </ignoredErrors>
 </worksheet>
 </file>